--- a/artfynd/A 33955-2026 artfynd.xlsx
+++ b/artfynd/A 33955-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127285</v>
       </c>
       <c r="B2" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136127662</v>
       </c>
       <c r="B3" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136129359</v>
       </c>
       <c r="B4" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136127498</v>
       </c>
       <c r="B6" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136127726</v>
       </c>
       <c r="B7" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136127866</v>
       </c>
       <c r="B8" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136127969</v>
       </c>
       <c r="B9" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136129097</v>
       </c>
       <c r="B10" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136129146</v>
       </c>
       <c r="B11" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>136129217</v>
       </c>
       <c r="B12" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>136129313</v>
       </c>
       <c r="B13" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136129466</v>
       </c>
       <c r="B14" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136129503</v>
       </c>
       <c r="B15" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136129379</v>
       </c>
       <c r="B16" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136127467</v>
       </c>
       <c r="B24" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>136128577</v>
       </c>
       <c r="B25" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>136128639</v>
       </c>
       <c r="B26" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>136128691</v>
       </c>
       <c r="B27" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>136129544</v>
       </c>
       <c r="B28" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>136129558</v>
       </c>
       <c r="B29" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 33955-2026 artfynd.xlsx
+++ b/artfynd/A 33955-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127285</v>
       </c>
       <c r="B2" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136127662</v>
       </c>
       <c r="B3" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136129359</v>
       </c>
       <c r="B4" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136127498</v>
       </c>
       <c r="B6" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136127726</v>
       </c>
       <c r="B7" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136127866</v>
       </c>
       <c r="B8" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136127969</v>
       </c>
       <c r="B9" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136129097</v>
       </c>
       <c r="B10" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136129146</v>
       </c>
       <c r="B11" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>136129217</v>
       </c>
       <c r="B12" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>136129313</v>
       </c>
       <c r="B13" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136129466</v>
       </c>
       <c r="B14" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136129503</v>
       </c>
       <c r="B15" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136129379</v>
       </c>
       <c r="B16" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136127467</v>
       </c>
       <c r="B24" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>136128577</v>
       </c>
       <c r="B25" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>136128639</v>
       </c>
       <c r="B26" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>136128691</v>
       </c>
       <c r="B27" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>136129544</v>
       </c>
       <c r="B28" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>136129558</v>
       </c>
       <c r="B29" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 33955-2026 artfynd.xlsx
+++ b/artfynd/A 33955-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136127285</v>
       </c>
       <c r="B2" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136127662</v>
       </c>
       <c r="B3" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136129359</v>
       </c>
       <c r="B4" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136127498</v>
       </c>
       <c r="B6" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136127726</v>
       </c>
       <c r="B7" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136127866</v>
       </c>
       <c r="B8" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136127969</v>
       </c>
       <c r="B9" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136129097</v>
       </c>
       <c r="B10" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>136129146</v>
       </c>
       <c r="B11" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>136129217</v>
       </c>
       <c r="B12" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>136129313</v>
       </c>
       <c r="B13" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136129466</v>
       </c>
       <c r="B14" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136129503</v>
       </c>
       <c r="B15" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136129379</v>
       </c>
       <c r="B16" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>136127218</v>
       </c>
       <c r="B19" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>136127205</v>
       </c>
       <c r="B23" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>136127467</v>
       </c>
       <c r="B24" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>136128577</v>
       </c>
       <c r="B25" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>136128639</v>
       </c>
       <c r="B26" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>136128691</v>
       </c>
       <c r="B27" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>136129544</v>
       </c>
       <c r="B28" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>136129558</v>
       </c>
       <c r="B29" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
